--- a/src/excel_master/assets/templates/test-case.xlsx
+++ b/src/excel_master/assets/templates/test-case.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,12 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,9 +70,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,42 +457,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>用例编号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>所属模块</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>用例标题</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>操作步骤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
